--- a/data/username.xlsx
+++ b/data/username.xlsx
@@ -14,12 +14,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Utilisateur</t>
   </si>
   <si>
     <t>Mots de Passe</t>
+  </si>
+  <si>
+    <t>dondonedmond</t>
+  </si>
+  <si>
+    <t>toor</t>
   </si>
 </sst>
 </file>
@@ -377,10 +383,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:3">
+    <row r="1" spans="1:3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -388,6 +394,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/username.xlsx
+++ b/data/username.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>Utilisateur</t>
   </si>
@@ -23,6 +23,9 @@
   </si>
   <si>
     <t>dondonedmond</t>
+  </si>
+  <si>
+    <t>dondonserge</t>
   </si>
   <si>
     <t>toor</t>
@@ -383,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,7 +405,18 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/username.xlsx
+++ b/data/username.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
     <t>Utilisateur</t>
   </si>
@@ -22,10 +22,19 @@
     <t>Mots de Passe</t>
   </si>
   <si>
+    <t>administrateur</t>
+  </si>
+  <si>
     <t>dondonedmond</t>
   </si>
   <si>
+    <t>dondonlukas</t>
+  </si>
+  <si>
     <t>dondonserge</t>
+  </si>
+  <si>
+    <t>admin</t>
   </si>
   <si>
     <t>toor</t>
@@ -386,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -405,7 +414,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -416,7 +425,29 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
         <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
